--- a/Intake_FireCatFull_v1.xlsx
+++ b/Intake_FireCatFull_v1.xlsx
@@ -21,8 +21,9 @@
     <sheet name="08. Splits Fire" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="08. Splits EQ" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="08. Splits Wind" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="06. EQ Aggs" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="07. Wind Aggs" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="09. Rate Development" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="06. EQ Aggs" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="07. Wind Aggs" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,8 +32,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -138,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +166,8 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:AK178"/>
+  <dimension ref="B1:AK182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1853,71 +1858,96 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>09. Rate Development</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>09 Rate</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Rate (optional)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Rate change (optional)</t>
+        </is>
+      </c>
+      <c r="X20" s="6" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="Y20" s="6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>Rate change basis</t>
+        </is>
+      </c>
+      <c r="AA20" s="6" t="inlineStr">
+        <is>
+          <t>As at</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>⟦INVENTORY⟧</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Holds</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>State</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Premium and loss history per section</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>EPI Projections</t>
+          <t>History</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Estimated premium income, N and N+1</t>
+          <t>Premium and loss history per section</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1929,17 +1959,17 @@
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Large Losses</t>
+          <t>EPI Projections</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Individual large claims, per-risk sections</t>
+          <t>Estimated premium income, N and N+1</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1951,17 +1981,17 @@
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Cat Losses</t>
+          <t>Large Losses</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Catastrophe events, cat sections</t>
+          <t>Individual large claims, per-risk sections</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1973,17 +2003,17 @@
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Risk Profiles</t>
+          <t>Cat Losses</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Banded exposure — the per-risk rating basis</t>
+          <t>Catastrophe events, cat sections</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1995,17 +2025,17 @@
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>EQ Aggs</t>
+          <t>Risk Profiles</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Earthquake sums insured per cat zone</t>
+          <t>Banded exposure — the per-risk rating basis</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2017,17 +2047,17 @@
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Wind Aggs</t>
+          <t>EQ Aggs</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Windstorm sums insured per cat zone</t>
+          <t>Earthquake sums insured per cat zone</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2039,17 +2069,17 @@
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Splits</t>
+          <t>Wind Aggs</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>The cedent's book split — sums insured, one block per section</t>
+          <t>Windstorm sums insured per cat zone</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2061,61 +2091,61 @@
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>08</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Rate Development</t>
+          <t>Splits</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Rate change history — optional</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>The cedent's book split — sums insured, one block per section</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>09</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Triangles</t>
+          <t>Rate Development</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Loss development triangles</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>The rate change a submission claims — the UW's own sheet</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Exchange rates</t>
+          <t>Triangles</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>FX rates for conversion between currencies</t>
+          <t>Loss development triangles</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -2127,181 +2157,193 @@
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Exchange rates</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>FX rates for conversion between currencies</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Collected step-2 blocks — written, never read</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>outstanding</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Every dataset the tool knows, whether or not this pack carries it. The register above lists what is here; ⟦SECTIONS⟧ says which roles each section expects, so a missing sheet reads as structure rather than as a gap.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="3" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>⟦SECTIONS⟧</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="7" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Datasets</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>01, 02, 03, 05, 08</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Earthquake</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>per risk</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04, 06, 08</t>
+          <t>01, 02, 03, 05, 08, 09</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
+          <t>Earthquake</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04, 06, 08, 09</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
           <t>Windstorm</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>01, 02, 04, 07, 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="2" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04, 07, 08, 09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>A section is a block. Per-risk sections carry large losses (03); cat sections carry event losses (04) instead. Rules are scoped by kind and evaluated once per applicable section, so an absent dataset is 'not applicable', not a gap.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="7" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Actual year</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="n">
-        <v>2025</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Treaty type</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Fire + Nat Cat, complete</t>
-        </is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
+          <t>Treaty type</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Example Insurance SA</t>
+          <t>Fire + Nat Cat, complete</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Loss share warning</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="n">
-        <v>0.2</v>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Rate change warning</t>
+          <t>Loss share warning</t>
         </is>
       </c>
       <c r="C53" s="10" t="n">
@@ -2311,248 +2353,208 @@
     <row r="54">
       <c r="B54" s="4" t="inlineStr">
         <is>
+          <t>Rate change warning</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="4" t="inlineStr">
+        <is>
           <t>Split view warning</t>
         </is>
       </c>
-      <c r="C54" s="10" t="n">
+      <c r="C55" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Rate claim warning</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="3" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>⟦ZONES⟧</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="7" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>Scheme</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Zones</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="6" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>EU EQ</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 6, 7, 8, 9a, 9b, 10, 11, 12</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="6" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>EU Wind</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 6, 7, 8</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>The complete zoning. Zones the cedent does not list are shown as 0 — absent reads as 'no data', zero reads as 'nothing there'.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="3" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>⟦AXES⟧</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="7" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>Axis</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Categories</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>06 EQ Aggs</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>Res, Com, Ind</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>06 EQ Aggs</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Cover</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Building, Content, BI</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="4" t="inlineStr">
         <is>
+          <t>06 EQ Aggs</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Res, Com, Ind</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>06 EQ Aggs</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Cover</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Building, Content, BI</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
           <t>07 Wind Aggs</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>Res, Com, Ind</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>The target cells of a dataset are the product of its axes. Found by position, not by name — renaming one changes no code (§2.6).</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="3" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>⟦SPLITS⟧</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="7" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>Axis</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t>Renewables</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Ind</t>
-        </is>
-      </c>
-      <c r="F75" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>House convention</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>Projects</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>Com</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>House convention</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2571,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Renewables</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -2578,7 +2580,7 @@
         </is>
       </c>
       <c r="F77" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
@@ -2599,7 +2601,7 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Projects</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -2608,7 +2610,7 @@
         </is>
       </c>
       <c r="F78" s="10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
@@ -2629,89 +2631,125 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>House convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Com</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>House convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>Ind</t>
         </is>
       </c>
-      <c r="F79" s="10" t="n">
+      <c r="F81" s="10" t="n">
         <v>0.25</v>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>House convention</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Only what is our judgement. Everything the cedent supplies comes from 08 and carries its own provenance.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="3" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="7" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Incurred Losses</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -2723,19 +2761,19 @@
     <row r="91">
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Band from</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -2747,19 +2785,19 @@
     <row r="93">
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Band to</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Band from</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -2771,7 +2809,7 @@
     <row r="95">
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Exposure</t>
+          <t>Band to</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -2783,31 +2821,31 @@
     <row r="96">
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -2819,7 +2857,7 @@
     <row r="99">
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Name of Loss</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -2831,55 +2869,55 @@
     <row r="100">
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Number of Claims</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Number of Claims</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Event End Date</t>
+          <t>Date of Loss</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -2891,55 +2929,55 @@
     <row r="105">
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Event Date</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Event End Date</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Res Building</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Res Content</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
@@ -2951,7 +2989,7 @@
     <row r="110">
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Res BI</t>
+          <t>Rate</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -2963,7 +3001,7 @@
     <row r="111">
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Com Building</t>
+          <t>Rate change</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -2975,7 +3013,7 @@
     <row r="112">
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Com Content</t>
+          <t>Res Building</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
@@ -2987,7 +3025,7 @@
     <row r="113">
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Com BI</t>
+          <t>Res Content</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
@@ -2999,7 +3037,7 @@
     <row r="114">
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Ind Building</t>
+          <t>Res BI</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
@@ -3011,7 +3049,7 @@
     <row r="115">
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Ind Content</t>
+          <t>Com Building</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
@@ -3023,7 +3061,7 @@
     <row r="116">
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Ind BI</t>
+          <t>Com Content</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
@@ -3035,7 +3073,7 @@
     <row r="117">
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Res</t>
+          <t>Com BI</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -3047,7 +3085,7 @@
     <row r="118">
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Com</t>
+          <t>Ind Building</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -3059,7 +3097,7 @@
     <row r="119">
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Ind</t>
+          <t>Ind Content</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -3071,7 +3109,7 @@
     <row r="120">
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Building</t>
+          <t>Ind BI</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -3083,7 +3121,7 @@
     <row r="121">
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Res</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -3095,7 +3133,7 @@
     <row r="122">
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>BI</t>
+          <t>Com</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -3107,7 +3145,7 @@
     <row r="123">
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Projects</t>
+          <t>Ind</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -3119,489 +3157,377 @@
     <row r="124">
       <c r="B124" s="4" t="inlineStr">
         <is>
+          <t>Building</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Projects</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="4" t="inlineStr">
+        <is>
           <t>Renewables</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" s="2" t="inlineStr">
+    <row r="130">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook.</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="B128" s="3" t="inlineStr">
+    <row r="132">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" s="7" t="inlineStr">
+    <row r="133">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>PF transfer</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
-        <is>
-          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Includes fac</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>yes | no</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Layered business</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>included | excluded</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Includes fac</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>yes | no</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Layered business</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>included | excluded</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="4" t="inlineStr">
         <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="B144" s="3" t="inlineStr">
+    <row r="148">
+      <c r="B148" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="B145" s="7" t="inlineStr">
+    <row r="149">
+      <c r="B149" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="B147" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>9 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>re-est</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>at inception</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="B150" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>re-est</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>at inception</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C154" s="5" t="inlineStr">
         <is>
           <t>at expiry</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="B152" s="2" t="inlineStr">
+    <row r="156">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="B154" s="3" t="inlineStr">
+    <row r="158">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D155" s="7" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H155" s="7" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I155" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C156" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D156" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H156" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C157" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
-        </is>
-      </c>
-      <c r="D157" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E157" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H157" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C158" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="D158" s="7" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E158" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H158" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C159" s="12" t="inlineStr">
-        <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E159" s="12" t="inlineStr">
-        <is>
-          <t>01.Incurred Losses@{Y}</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H159" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I159" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="7" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C160" s="12" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D160" s="7" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F160" s="4" t="n">
@@ -3614,24 +3540,24 @@
       </c>
       <c r="H160" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>01.Premium@{N}</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
@@ -3641,11 +3567,11 @@
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>03.Year basis</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F161" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
@@ -3654,34 +3580,34 @@
       </c>
       <c r="H161" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>R-10</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C162" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>04.Year basis</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F162" s="4" t="n">
@@ -3694,151 +3620,311 @@
       </c>
       <c r="H162" s="5" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>SUM(03.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>large losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E165" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>04.Year basis</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="B164" s="2" t="inlineStr">
+    <row r="168">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="B166" s="3" t="inlineStr">
+    <row r="170">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="B167" s="7" t="inlineStr">
+    <row r="171">
+      <c r="B171" s="7" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr">
+      <c r="C171" s="7" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="B168" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="B169" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="B170" s="13" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="B171" s="13" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;row&gt;</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="13" t="inlineStr">
         <is>
+          <t>Transpose_i</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>block i is transposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="13" t="inlineStr">
+        <is>
+          <t>Dataset_i = &lt;key&gt;</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="13" t="inlineStr">
+        <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C180" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="B178" s="7" t="inlineStr">
+    <row r="182">
+      <c r="B182" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -5320,6 +5406,347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>09. Rate Development — underwriter's own</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>— Fire —</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Scope_1 = Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Source_1 = cedent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Rate change basis_1 = risk-adjusted</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>As at_1 = 30.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>U/W year</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Rate %o</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G9" s="20">
+        <f>ROW()</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>1.215</v>
+      </c>
+      <c r="G10" s="20">
+        <f>ROW()</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="G11" s="20">
+        <f>ROW()</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="G12" s="20">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="G13" s="20">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Info_1 = G</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>— Earthquake + Windstorm —</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Scope_2 = Earthquake + Windstorm</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Source_2 = broker</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Rate change basis_2 = nominal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>As at_2 = 30.09.2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>U/W year</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Change vs prior</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Header_2</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Rate change</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="G23" s="20">
+        <f>ROW()</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G24" s="20">
+        <f>ROW()</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G25" s="20">
+        <f>ROW()</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G26" s="20">
+        <f>ROW()</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Info_2 = G</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6546,7 +6973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Intake_FireCatFull_v1.xlsx
+++ b/Intake_FireCatFull_v1.xlsx
@@ -34,7 +34,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000%"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Rate %o</t>
+          <t>Tasa %</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="C9" s="24" t="n">
-        <v>1.18</v>
+        <v>0.00118</v>
       </c>
       <c r="G9" s="20">
         <f>ROW()</f>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="C10" s="24" t="n">
-        <v>1.215</v>
+        <v>0.001215</v>
       </c>
       <c r="G10" s="20">
         <f>ROW()</f>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>1.288</v>
+        <v>0.001288</v>
       </c>
       <c r="G11" s="20">
         <f>ROW()</f>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="C12" s="24" t="n">
-        <v>1.352</v>
+        <v>0.001352</v>
       </c>
       <c r="G12" s="20">
         <f>ROW()</f>
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="C13" s="24" t="n">
-        <v>1.406</v>
+        <v>0.001406</v>
       </c>
       <c r="G13" s="20">
         <f>ROW()</f>
